--- a/Kanedata.xlsx
+++ b/Kanedata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4582BDF1-9A77-45D1-BC27-98FD737DE3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0746B23F-F006-47BB-9694-28C3D194E3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="336" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="384" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>

--- a/Kanedata.xlsx
+++ b/Kanedata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0746B23F-F006-47BB-9694-28C3D194E3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAA7BB-46DA-4A95-BAB0-381FB2AA70BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="384" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="150" windowWidth="24060" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="55">
   <si>
     <t>AConstant</t>
   </si>
@@ -67,10 +67,6 @@
     <t>Sex</t>
   </si>
   <si>
-    <t>M</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Target refraction</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -87,6 +83,132 @@
   </si>
   <si>
     <t>ACD_OD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KALA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>attack02</t>
+  </si>
+  <si>
+    <t>attack03</t>
+  </si>
+  <si>
+    <t>attack04</t>
+  </si>
+  <si>
+    <t>attack05</t>
+  </si>
+  <si>
+    <t>attack06</t>
+  </si>
+  <si>
+    <t>attack07</t>
+  </si>
+  <si>
+    <t>attack08</t>
+  </si>
+  <si>
+    <t>attack09</t>
+  </si>
+  <si>
+    <t>attack10</t>
+  </si>
+  <si>
+    <t>attack11</t>
+  </si>
+  <si>
+    <t>attack12</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>attack13</t>
+  </si>
+  <si>
+    <t>attack14</t>
+  </si>
+  <si>
+    <t>attack15</t>
+  </si>
+  <si>
+    <t>attack16</t>
+  </si>
+  <si>
+    <t>attack17</t>
+  </si>
+  <si>
+    <t>attack18</t>
+  </si>
+  <si>
+    <t>attack19</t>
+  </si>
+  <si>
+    <t>attack20</t>
+  </si>
+  <si>
+    <t>attack21</t>
+  </si>
+  <si>
+    <t>attack22</t>
+  </si>
+  <si>
+    <t>attack23</t>
+  </si>
+  <si>
+    <t>attack24</t>
+  </si>
+  <si>
+    <t>attack25</t>
+  </si>
+  <si>
+    <t>attack26</t>
+  </si>
+  <si>
+    <t>attack27</t>
+  </si>
+  <si>
+    <t>attack28</t>
+  </si>
+  <si>
+    <t>attack29</t>
+  </si>
+  <si>
+    <t>attack30</t>
+  </si>
+  <si>
+    <t>attack31</t>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>attack32</t>
+  </si>
+  <si>
+    <t>attack33</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>attack34</t>
+  </si>
+  <si>
+    <t>attack35</t>
+  </si>
+  <si>
+    <t>attack36</t>
+  </si>
+  <si>
+    <t>KALF</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -94,10 +216,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -137,12 +260,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,7 +292,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -192,7 +321,46 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -502,8 +670,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="4" width="13" style="2" customWidth="1"/>
@@ -515,7 +683,7 @@
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -523,108 +691,2648 @@
         <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1">
         <v>105737</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="9">
-        <v>118.99</v>
-      </c>
-      <c r="F2" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="7">
         <v>23.33</v>
       </c>
-      <c r="H2" s="7">
+      <c r="J2" s="7">
+        <v>44.75</v>
+      </c>
+      <c r="K2" s="7">
         <v>44.25</v>
       </c>
-      <c r="I2" s="7">
+      <c r="L2" s="7">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="M2" s="13">
+        <v>21.5</v>
+      </c>
+      <c r="N2" s="13"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="1"/>
+      <c r="C3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1">
+        <v>133873</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H3" s="12">
+        <v>-0.36</v>
+      </c>
+      <c r="I3" s="7">
+        <v>23.17</v>
+      </c>
+      <c r="J3" s="7">
+        <v>43.75</v>
+      </c>
+      <c r="K3" s="7">
+        <v>44.5</v>
+      </c>
+      <c r="L3" s="7">
+        <v>1.81</v>
+      </c>
+      <c r="M3" s="13">
+        <v>22</v>
+      </c>
+      <c r="N3" s="13"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1">
+        <v>132594</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H4" s="12">
+        <v>-0.87</v>
+      </c>
+      <c r="I4" s="7">
+        <v>21.64</v>
+      </c>
+      <c r="J4" s="7">
+        <v>46.75</v>
+      </c>
+      <c r="K4" s="7">
+        <v>48.5</v>
+      </c>
+      <c r="L4" s="7">
+        <v>2.73</v>
+      </c>
+      <c r="M4" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1">
+        <v>133854</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H5" s="12">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="J5" s="7">
+        <v>47.75</v>
+      </c>
+      <c r="K5" s="7">
+        <v>48.5</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1.98</v>
+      </c>
+      <c r="M5" s="13">
+        <v>27.5</v>
+      </c>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1">
+        <v>35135</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H6" s="12">
+        <v>-0.13</v>
+      </c>
+      <c r="I6" s="7">
+        <v>22.59</v>
+      </c>
+      <c r="J6" s="7">
+        <v>42.56</v>
+      </c>
+      <c r="K6" s="7">
+        <v>43.44</v>
+      </c>
+      <c r="L6" s="7">
+        <v>3.16</v>
+      </c>
+      <c r="M6" s="13">
+        <v>25.5</v>
+      </c>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1">
+        <v>23574</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="11">
+        <v>118.5</v>
+      </c>
+      <c r="H7" s="12">
+        <v>-0.97</v>
+      </c>
+      <c r="I7" s="7">
+        <v>23.08</v>
+      </c>
+      <c r="J7" s="7">
+        <v>42.45</v>
+      </c>
+      <c r="K7" s="7">
+        <v>43.77</v>
+      </c>
+      <c r="L7" s="7">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="M7" s="13">
+        <v>23.5</v>
+      </c>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1">
+        <v>143993</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H8" s="12">
+        <v>-0.6</v>
+      </c>
+      <c r="I8" s="7">
+        <v>23.28</v>
+      </c>
+      <c r="J8" s="7">
+        <v>43.05</v>
+      </c>
+      <c r="K8" s="7">
+        <v>44.41</v>
+      </c>
+      <c r="L8" s="7">
+        <v>2.27</v>
+      </c>
+      <c r="M8" s="13">
+        <v>22.5</v>
+      </c>
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1">
+        <v>47248</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H9" s="12">
+        <v>-0.79</v>
+      </c>
+      <c r="I9" s="7">
+        <v>22.35</v>
+      </c>
+      <c r="J9" s="7">
+        <v>43.44</v>
+      </c>
+      <c r="K9" s="7">
+        <v>44.7</v>
+      </c>
+      <c r="L9" s="7">
+        <v>2.06</v>
+      </c>
+      <c r="M9" s="13">
+        <v>26</v>
+      </c>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1">
+        <v>110627</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H10" s="12">
+        <v>-0.65</v>
+      </c>
+      <c r="I10" s="7">
+        <v>22.05</v>
+      </c>
+      <c r="J10" s="7">
+        <v>43.72</v>
+      </c>
+      <c r="K10" s="7">
+        <v>45.3</v>
+      </c>
+      <c r="L10" s="7">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="M10" s="13">
+        <v>26.5</v>
+      </c>
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1">
+        <v>161460</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H11" s="12">
+        <v>-1.03</v>
+      </c>
+      <c r="I11" s="7">
+        <v>23.85</v>
+      </c>
+      <c r="J11" s="7">
+        <v>41.62</v>
+      </c>
+      <c r="K11" s="7">
+        <v>43.16</v>
+      </c>
+      <c r="L11" s="7">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="M11" s="13">
+        <v>23</v>
+      </c>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1">
+        <v>161554</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H12" s="12">
+        <v>-0.31</v>
+      </c>
+      <c r="I12" s="7">
+        <v>21.48</v>
+      </c>
+      <c r="J12" s="7">
+        <v>44.64</v>
+      </c>
+      <c r="K12" s="7">
+        <v>46.81</v>
+      </c>
+      <c r="L12" s="7">
+        <v>2.37</v>
+      </c>
+      <c r="M12" s="13">
+        <v>26.5</v>
+      </c>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1">
+        <v>166237</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="7">
+        <v>22.09</v>
+      </c>
+      <c r="J13" s="7">
+        <v>44.76</v>
+      </c>
+      <c r="K13" s="7">
+        <v>45.61</v>
+      </c>
+      <c r="L13" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="M13" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1">
+        <v>166886</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H14" s="12">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="I14" s="7">
+        <v>23.09</v>
+      </c>
+      <c r="J14" s="7">
+        <v>41.56</v>
+      </c>
+      <c r="K14" s="7">
+        <v>42.51</v>
+      </c>
+      <c r="L14" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M14" s="13">
+        <v>25</v>
+      </c>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1">
+        <v>167592</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H15" s="12">
+        <v>-0.86</v>
+      </c>
+      <c r="I15" s="7">
+        <v>22.37</v>
+      </c>
+      <c r="J15" s="7">
+        <v>43.44</v>
+      </c>
+      <c r="K15" s="7">
+        <v>45.67</v>
+      </c>
+      <c r="L15" s="7">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="M15" s="13">
+        <v>25.5</v>
+      </c>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1">
+        <v>51973</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H16" s="12">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="I16" s="7">
+        <v>21.76</v>
+      </c>
+      <c r="J16" s="7">
+        <v>44.76</v>
+      </c>
+      <c r="K16" s="7">
+        <v>47.47</v>
+      </c>
+      <c r="L16" s="7">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="M16" s="13">
+        <v>26</v>
+      </c>
+      <c r="N16" s="13"/>
+    </row>
+    <row r="17" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1">
+        <v>145550</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H17" s="12">
+        <v>-0.43</v>
+      </c>
+      <c r="I17" s="7">
+        <v>22.2</v>
+      </c>
+      <c r="J17" s="7">
+        <v>44.41</v>
+      </c>
+      <c r="K17" s="7">
+        <v>44.76</v>
+      </c>
+      <c r="L17" s="7">
+        <v>2.35</v>
+      </c>
+      <c r="M17" s="13">
+        <v>25.5</v>
+      </c>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1">
+        <v>173959</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="11">
+        <v>119.49</v>
+      </c>
+      <c r="H18" s="12">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="I18" s="7">
+        <v>22.56</v>
+      </c>
+      <c r="J18" s="7">
+        <v>43.49</v>
+      </c>
+      <c r="K18" s="7">
+        <v>44.18</v>
+      </c>
+      <c r="L18" s="7">
+        <v>2.33</v>
+      </c>
+      <c r="M18" s="13">
+        <v>25.5</v>
+      </c>
+      <c r="N18" s="13"/>
+    </row>
+    <row r="19" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1">
+        <v>174163</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H19" s="12">
+        <v>-0.85</v>
+      </c>
+      <c r="I19" s="7">
+        <v>22.33</v>
+      </c>
+      <c r="J19" s="7">
+        <v>43.44</v>
+      </c>
+      <c r="K19" s="7">
+        <v>45.24</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="M19" s="13">
+        <v>25.5</v>
+      </c>
+      <c r="N19" s="13"/>
+    </row>
+    <row r="20" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28886</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H20" s="12">
+        <v>-0.12</v>
+      </c>
+      <c r="I20" s="7">
+        <v>21.66</v>
+      </c>
+      <c r="J20" s="7">
+        <v>46.36</v>
+      </c>
+      <c r="K20" s="7">
+        <v>47.67</v>
+      </c>
+      <c r="L20" s="7">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="M20" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="N20" s="13"/>
+    </row>
+    <row r="21" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1">
+        <v>177432</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H21" s="12">
+        <v>-0.66</v>
+      </c>
+      <c r="I21" s="7">
+        <v>22.9</v>
+      </c>
+      <c r="J21" s="7">
+        <v>44.7</v>
+      </c>
+      <c r="K21" s="7">
+        <v>45.61</v>
+      </c>
+      <c r="L21" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M21" s="13">
+        <v>22.5</v>
+      </c>
+      <c r="N21" s="13"/>
+    </row>
+    <row r="22" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1">
+        <v>178621</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H22" s="12">
+        <v>-0.61</v>
+      </c>
+      <c r="I22" s="7">
+        <v>22.21</v>
+      </c>
+      <c r="J22" s="7">
+        <v>45.98</v>
+      </c>
+      <c r="K22" s="7">
+        <v>46.87</v>
+      </c>
+      <c r="L22" s="7">
+        <v>2.13</v>
+      </c>
+      <c r="M22" s="13">
+        <v>23.5</v>
+      </c>
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1">
+        <v>178965</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H23" s="12">
+        <v>-1.08</v>
+      </c>
+      <c r="I23" s="7">
+        <v>22.11</v>
+      </c>
+      <c r="J23" s="7">
+        <v>43.95</v>
+      </c>
+      <c r="K23" s="7">
+        <v>44.23</v>
+      </c>
+      <c r="L23" s="7">
+        <v>2.19</v>
+      </c>
+      <c r="M23" s="13">
+        <v>27</v>
+      </c>
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1">
+        <v>184985</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H24" s="12">
+        <v>-0.84</v>
+      </c>
+      <c r="I24" s="7">
+        <v>22.11</v>
+      </c>
+      <c r="J24" s="7">
+        <v>43.55</v>
+      </c>
+      <c r="K24" s="7">
+        <v>45.79</v>
+      </c>
+      <c r="L24" s="7">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="M24" s="13">
+        <v>26</v>
+      </c>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1">
+        <v>186160</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H25" s="12">
+        <v>-0.1</v>
+      </c>
+      <c r="I25" s="7">
+        <v>22.51</v>
+      </c>
+      <c r="J25" s="7">
+        <v>45.12</v>
+      </c>
+      <c r="K25" s="7">
+        <v>45.42</v>
+      </c>
+      <c r="L25" s="7">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="M25" s="13">
+        <v>23</v>
+      </c>
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="1">
+        <v>96698</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H26" s="12">
+        <v>-1.43</v>
+      </c>
+      <c r="I26" s="7">
+        <v>23.71</v>
+      </c>
+      <c r="J26" s="7">
+        <v>44.29</v>
+      </c>
+      <c r="K26" s="7">
+        <v>44.58</v>
+      </c>
+      <c r="L26" s="7">
+        <v>2.69</v>
+      </c>
+      <c r="M26" s="13">
+        <v>21.5</v>
+      </c>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1">
+        <v>125842</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0.41</v>
+      </c>
+      <c r="I27" s="7">
+        <v>21.24</v>
+      </c>
+      <c r="J27" s="7">
+        <v>43.5</v>
+      </c>
+      <c r="K27" s="7">
+        <v>46</v>
+      </c>
+      <c r="L27" s="7">
+        <v>2.75</v>
+      </c>
+      <c r="M27" s="13">
+        <v>28</v>
+      </c>
+      <c r="N27" s="13"/>
+    </row>
+    <row r="28" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1">
+        <v>192766</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="11">
+        <v>119.49</v>
+      </c>
+      <c r="H28" s="12">
+        <v>0.11</v>
+      </c>
+      <c r="I28" s="7">
+        <v>22.43</v>
+      </c>
+      <c r="J28" s="7">
+        <v>44.9</v>
+      </c>
+      <c r="K28" s="7">
+        <v>45.3</v>
+      </c>
+      <c r="L28" s="7">
+        <v>2.48</v>
+      </c>
+      <c r="M28" s="13">
+        <v>23.5</v>
+      </c>
+      <c r="N28" s="13"/>
+    </row>
+    <row r="29" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1">
+        <v>193016</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H29" s="12">
+        <v>-1.43</v>
+      </c>
+      <c r="I29" s="7">
+        <v>22.38</v>
+      </c>
+      <c r="J29" s="7">
+        <v>45.5</v>
+      </c>
+      <c r="K29" s="7">
+        <v>46</v>
+      </c>
+      <c r="L29" s="7">
+        <v>2.62</v>
+      </c>
+      <c r="M29" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="N29" s="13"/>
+    </row>
+    <row r="30" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="1">
+        <v>10137</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H30" s="12">
+        <v>-0.72</v>
+      </c>
+      <c r="I30" s="7">
+        <v>22.91</v>
+      </c>
+      <c r="J30" s="7">
+        <v>44.47</v>
+      </c>
+      <c r="K30" s="7">
+        <v>45.49</v>
+      </c>
+      <c r="L30" s="7">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="M30" s="13">
+        <v>22.5</v>
+      </c>
+      <c r="N30" s="13"/>
+    </row>
+    <row r="31" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="1">
+        <v>198772</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H31" s="12">
+        <v>-0.52</v>
+      </c>
+      <c r="I31" s="7">
+        <v>22.02</v>
+      </c>
+      <c r="J31" s="7">
+        <v>42.61</v>
+      </c>
+      <c r="K31" s="7">
+        <v>43.32</v>
+      </c>
+      <c r="L31" s="7">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="M31" s="13">
+        <v>28.5</v>
+      </c>
+      <c r="N31" s="13"/>
+    </row>
+    <row r="32" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="1">
+        <v>115099</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H32" s="12">
+        <v>-0.8</v>
+      </c>
+      <c r="I32" s="7">
+        <v>22.93</v>
+      </c>
+      <c r="J32" s="7">
+        <v>45.12</v>
+      </c>
+      <c r="K32" s="7">
+        <v>45.79</v>
+      </c>
+      <c r="L32" s="7">
+        <v>2.41</v>
+      </c>
+      <c r="M32" s="13">
+        <v>22</v>
+      </c>
+      <c r="N32" s="13"/>
+    </row>
+    <row r="33" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="1">
+        <v>207268</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H33" s="12">
+        <v>-0.06</v>
+      </c>
+      <c r="I33" s="7">
+        <v>23.14</v>
+      </c>
+      <c r="J33" s="7">
+        <v>41.82</v>
+      </c>
+      <c r="K33" s="7">
+        <v>42.19</v>
+      </c>
+      <c r="L33" s="7">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M33" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="N33" s="13"/>
+    </row>
+    <row r="34" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C34" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="10">
+        <v>209451</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H34" s="10">
+        <v>-0.04</v>
+      </c>
+      <c r="I34" s="6">
+        <v>22.95</v>
+      </c>
+      <c r="J34" s="6">
+        <v>43.72</v>
+      </c>
+      <c r="K34" s="6">
+        <v>44.06</v>
+      </c>
+      <c r="L34" s="6">
+        <v>2.27</v>
+      </c>
+      <c r="M34" s="14">
+        <v>23</v>
+      </c>
+      <c r="N34" s="14"/>
+    </row>
+    <row r="35" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C35" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="10">
+        <v>46462</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="11">
+        <v>119.36</v>
+      </c>
+      <c r="H35" s="10">
+        <v>-1.32</v>
+      </c>
+      <c r="I35" s="6">
+        <v>22.85</v>
+      </c>
+      <c r="J35" s="6">
+        <v>44.53</v>
+      </c>
+      <c r="K35" s="6">
+        <v>45.42</v>
+      </c>
+      <c r="L35" s="6">
+        <v>2.29</v>
+      </c>
+      <c r="M35" s="14">
+        <v>24</v>
+      </c>
+      <c r="N35" s="14"/>
+    </row>
+    <row r="36" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C36" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="10">
+        <v>129805</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H36" s="10">
+        <v>-1.06</v>
+      </c>
+      <c r="I36" s="6">
+        <v>21.15</v>
+      </c>
+      <c r="J36" s="6">
+        <v>44.23</v>
+      </c>
+      <c r="K36" s="6">
+        <v>44.94</v>
+      </c>
+      <c r="L36" s="6">
+        <v>2.27</v>
+      </c>
+      <c r="M36" s="14">
+        <v>30</v>
+      </c>
+      <c r="N36" s="14"/>
+    </row>
+    <row r="37" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C37" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="10">
+        <v>215513</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="11">
+        <v>118.98</v>
+      </c>
+      <c r="H37" s="10">
+        <v>-0.72</v>
+      </c>
+      <c r="I37" s="6">
+        <v>21.88</v>
+      </c>
+      <c r="J37" s="6">
+        <v>46.88</v>
+      </c>
+      <c r="K37" s="6">
+        <v>47.54</v>
+      </c>
+      <c r="L37" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="M37" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="N37" s="14"/>
+    </row>
+    <row r="38" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C38" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="16">
+        <v>105737</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H38" s="18">
+        <v>-0.61</v>
+      </c>
+      <c r="I38" s="6">
+        <v>23.04</v>
+      </c>
+      <c r="J38" s="18">
         <v>44.75</v>
       </c>
-      <c r="J2" s="7">
+      <c r="K38" s="18">
+        <v>44.25</v>
+      </c>
+      <c r="L38" s="18">
         <v>2.1800000000000002</v>
       </c>
-      <c r="K2" s="9">
+      <c r="M38" s="19">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="10"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="1"/>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="1"/>
-      <c r="D5" s="10"/>
-    </row>
-    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="1"/>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="1"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="1"/>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="1"/>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="1"/>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="1"/>
-      <c r="D11" s="10"/>
+      <c r="N38" s="19"/>
+    </row>
+    <row r="39" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="16">
+        <v>133873</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H39" s="18">
+        <v>-0.62</v>
+      </c>
+      <c r="I39" s="6">
+        <v>22.79</v>
+      </c>
+      <c r="J39" s="18">
+        <v>43.75</v>
+      </c>
+      <c r="K39" s="18">
+        <v>44.5</v>
+      </c>
+      <c r="L39" s="18">
+        <v>1.81</v>
+      </c>
+      <c r="M39" s="19">
+        <v>22</v>
+      </c>
+      <c r="N39" s="19"/>
+    </row>
+    <row r="40" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C40" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="16">
+        <v>132594</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H40" s="18">
+        <v>-0.84</v>
+      </c>
+      <c r="I40" s="6">
+        <v>21.68</v>
+      </c>
+      <c r="J40" s="18">
+        <v>46.75</v>
+      </c>
+      <c r="K40" s="18">
+        <v>48.5</v>
+      </c>
+      <c r="L40" s="18">
+        <v>2.73</v>
+      </c>
+      <c r="M40" s="19">
+        <v>24.5</v>
+      </c>
+      <c r="N40" s="19"/>
+    </row>
+    <row r="41" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="16">
+        <v>133854</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H41" s="18">
+        <v>-2.04</v>
+      </c>
+      <c r="I41" s="6">
+        <v>21.05</v>
+      </c>
+      <c r="J41" s="18">
+        <v>47.75</v>
+      </c>
+      <c r="K41" s="18">
+        <v>48.5</v>
+      </c>
+      <c r="L41" s="18">
+        <v>1.98</v>
+      </c>
+      <c r="M41" s="19">
+        <v>27.5</v>
+      </c>
+      <c r="N41" s="19"/>
+    </row>
+    <row r="42" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C42" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="16">
+        <v>35135</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H42" s="18">
+        <v>1.83</v>
+      </c>
+      <c r="I42" s="6">
+        <v>21.78</v>
+      </c>
+      <c r="J42" s="18">
+        <v>42.56</v>
+      </c>
+      <c r="K42" s="18">
+        <v>43.44</v>
+      </c>
+      <c r="L42" s="18">
+        <v>3.16</v>
+      </c>
+      <c r="M42" s="19">
+        <v>25.5</v>
+      </c>
+      <c r="N42" s="19"/>
+    </row>
+    <row r="43" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C43" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="16">
+        <v>23574</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="17">
+        <v>118.5</v>
+      </c>
+      <c r="H43" s="18">
+        <v>-0.85</v>
+      </c>
+      <c r="I43" s="6">
+        <v>23.04</v>
+      </c>
+      <c r="J43" s="18">
+        <v>42.45</v>
+      </c>
+      <c r="K43" s="18">
+        <v>43.77</v>
+      </c>
+      <c r="L43" s="18">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="M43" s="19">
+        <v>23.5</v>
+      </c>
+      <c r="N43" s="19"/>
+    </row>
+    <row r="44" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C44" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="16">
+        <v>143993</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H44" s="18">
+        <v>-2.73</v>
+      </c>
+      <c r="I44" s="6">
+        <v>24.09</v>
+      </c>
+      <c r="J44" s="18">
+        <v>43.05</v>
+      </c>
+      <c r="K44" s="18">
+        <v>44.41</v>
+      </c>
+      <c r="L44" s="18">
+        <v>2.27</v>
+      </c>
+      <c r="M44" s="19">
+        <v>22.5</v>
+      </c>
+      <c r="N44" s="19"/>
+    </row>
+    <row r="45" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C45" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="16">
+        <v>47248</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H45" s="18">
+        <v>-0.4</v>
+      </c>
+      <c r="I45" s="6">
+        <v>22.17</v>
+      </c>
+      <c r="J45" s="18">
+        <v>43.44</v>
+      </c>
+      <c r="K45" s="18">
+        <v>44.7</v>
+      </c>
+      <c r="L45" s="18">
+        <v>2.06</v>
+      </c>
+      <c r="M45" s="19">
+        <v>26</v>
+      </c>
+      <c r="N45" s="19"/>
+    </row>
+    <row r="46" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C46" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="16">
+        <v>110627</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H46" s="18">
+        <v>0.32</v>
+      </c>
+      <c r="I46" s="6">
+        <v>21.69</v>
+      </c>
+      <c r="J46" s="18">
+        <v>43.72</v>
+      </c>
+      <c r="K46" s="18">
+        <v>45.3</v>
+      </c>
+      <c r="L46" s="18">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="M46" s="19">
+        <v>26.5</v>
+      </c>
+      <c r="N46" s="19"/>
+    </row>
+    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="16">
+        <v>161460</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H47" s="18">
+        <v>-0.72</v>
+      </c>
+      <c r="I47" s="6">
+        <v>23.65</v>
+      </c>
+      <c r="J47" s="18">
+        <v>41.62</v>
+      </c>
+      <c r="K47" s="18">
+        <v>43.16</v>
+      </c>
+      <c r="L47" s="18">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="M47" s="19">
+        <v>23</v>
+      </c>
+      <c r="N47" s="19"/>
+    </row>
+    <row r="48" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C48" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" s="16">
+        <v>161554</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H48" s="18">
+        <v>-0.72</v>
+      </c>
+      <c r="I48" s="6">
+        <v>21.55</v>
+      </c>
+      <c r="J48" s="18">
+        <v>44.64</v>
+      </c>
+      <c r="K48" s="18">
+        <v>46.81</v>
+      </c>
+      <c r="L48" s="18">
+        <v>2.37</v>
+      </c>
+      <c r="M48" s="19">
+        <v>26.5</v>
+      </c>
+      <c r="N48" s="19"/>
+    </row>
+    <row r="49" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C49" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E49" s="16">
+        <v>166237</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G49" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H49" s="18">
+        <v>-1.33</v>
+      </c>
+      <c r="I49" s="6">
+        <v>22.41</v>
+      </c>
+      <c r="J49" s="18">
+        <v>44.76</v>
+      </c>
+      <c r="K49" s="18">
+        <v>45.61</v>
+      </c>
+      <c r="L49" s="18">
+        <v>2.11</v>
+      </c>
+      <c r="M49" s="19">
+        <v>24.5</v>
+      </c>
+      <c r="N49" s="19"/>
+    </row>
+    <row r="50" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C50" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="16">
+        <v>166886</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H50" s="18">
+        <v>0.41</v>
+      </c>
+      <c r="I50" s="6">
+        <v>22.79</v>
+      </c>
+      <c r="J50" s="18">
+        <v>41.56</v>
+      </c>
+      <c r="K50" s="18">
+        <v>42.51</v>
+      </c>
+      <c r="L50" s="18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M50" s="19">
+        <v>25</v>
+      </c>
+      <c r="N50" s="19"/>
+    </row>
+    <row r="51" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C51" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" s="16">
+        <v>167592</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H51" s="18">
+        <v>-1.67</v>
+      </c>
+      <c r="I51" s="6">
+        <v>22.61</v>
+      </c>
+      <c r="J51" s="18">
+        <v>43.44</v>
+      </c>
+      <c r="K51" s="18">
+        <v>45.67</v>
+      </c>
+      <c r="L51" s="18">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="M51" s="19">
+        <v>25.5</v>
+      </c>
+      <c r="N51" s="19"/>
+    </row>
+    <row r="52" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C52" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="16">
+        <v>51973</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H52" s="18">
+        <v>0.16</v>
+      </c>
+      <c r="I52" s="6">
+        <v>21.25</v>
+      </c>
+      <c r="J52" s="18">
+        <v>44.76</v>
+      </c>
+      <c r="K52" s="18">
+        <v>47.47</v>
+      </c>
+      <c r="L52" s="18">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="M52" s="19">
+        <v>26</v>
+      </c>
+      <c r="N52" s="19"/>
+    </row>
+    <row r="53" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C53" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="16">
+        <v>145550</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H53" s="18">
+        <v>-0.08</v>
+      </c>
+      <c r="I53" s="6">
+        <v>22.04</v>
+      </c>
+      <c r="J53" s="18">
+        <v>44.41</v>
+      </c>
+      <c r="K53" s="18">
+        <v>44.76</v>
+      </c>
+      <c r="L53" s="18">
+        <v>2.35</v>
+      </c>
+      <c r="M53" s="19">
+        <v>25.5</v>
+      </c>
+      <c r="N53" s="19"/>
+    </row>
+    <row r="54" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C54" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" s="16">
+        <v>173959</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="17">
+        <v>119.49</v>
+      </c>
+      <c r="H54" s="18">
+        <v>-1.35</v>
+      </c>
+      <c r="I54" s="6">
+        <v>22.75</v>
+      </c>
+      <c r="J54" s="18">
+        <v>43.49</v>
+      </c>
+      <c r="K54" s="18">
+        <v>44.18</v>
+      </c>
+      <c r="L54" s="18">
+        <v>2.33</v>
+      </c>
+      <c r="M54" s="19">
+        <v>25.5</v>
+      </c>
+      <c r="N54" s="19"/>
+    </row>
+    <row r="55" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C55" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" s="16">
+        <v>174163</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H55" s="18">
+        <v>-1.6</v>
+      </c>
+      <c r="I55" s="6">
+        <v>22.47</v>
+      </c>
+      <c r="J55" s="18">
+        <v>43.44</v>
+      </c>
+      <c r="K55" s="18">
+        <v>45.24</v>
+      </c>
+      <c r="L55" s="18">
+        <v>1.83</v>
+      </c>
+      <c r="M55" s="19">
+        <v>25.5</v>
+      </c>
+      <c r="N55" s="19"/>
+    </row>
+    <row r="56" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C56" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" s="16">
+        <v>28886</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H56" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="I56" s="6">
+        <v>21.53</v>
+      </c>
+      <c r="J56" s="18">
+        <v>46.36</v>
+      </c>
+      <c r="K56" s="18">
+        <v>47.67</v>
+      </c>
+      <c r="L56" s="18">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="M56" s="19">
+        <v>24.5</v>
+      </c>
+      <c r="N56" s="19"/>
+    </row>
+    <row r="57" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C57" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" s="16">
+        <v>177432</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-0.87</v>
+      </c>
+      <c r="I57" s="6">
+        <v>22.97</v>
+      </c>
+      <c r="J57" s="18">
+        <v>44.7</v>
+      </c>
+      <c r="K57" s="18">
+        <v>45.61</v>
+      </c>
+      <c r="L57" s="18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M57" s="19">
+        <v>22.5</v>
+      </c>
+      <c r="N57" s="19"/>
+    </row>
+    <row r="58" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C58" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="16">
+        <v>178621</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-0.02</v>
+      </c>
+      <c r="I58" s="6">
+        <v>21.95</v>
+      </c>
+      <c r="J58" s="18">
+        <v>45.98</v>
+      </c>
+      <c r="K58" s="18">
+        <v>46.87</v>
+      </c>
+      <c r="L58" s="18">
+        <v>2.13</v>
+      </c>
+      <c r="M58" s="19">
+        <v>23.5</v>
+      </c>
+      <c r="N58" s="19"/>
+    </row>
+    <row r="59" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C59" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" s="16">
+        <v>178965</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="I59" s="6">
+        <v>22.03</v>
+      </c>
+      <c r="J59" s="18">
+        <v>43.95</v>
+      </c>
+      <c r="K59" s="18">
+        <v>44.23</v>
+      </c>
+      <c r="L59" s="18">
+        <v>2.19</v>
+      </c>
+      <c r="M59" s="19">
+        <v>27</v>
+      </c>
+      <c r="N59" s="19"/>
+    </row>
+    <row r="60" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C60" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E60" s="16">
+        <v>184985</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H60" s="18">
+        <v>0.52</v>
+      </c>
+      <c r="I60" s="6">
+        <v>21.58</v>
+      </c>
+      <c r="J60" s="18">
+        <v>43.55</v>
+      </c>
+      <c r="K60" s="18">
+        <v>45.79</v>
+      </c>
+      <c r="L60" s="18">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="M60" s="19">
+        <v>26</v>
+      </c>
+      <c r="N60" s="19"/>
+    </row>
+    <row r="61" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C61" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="16">
+        <v>186160</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-0.06</v>
+      </c>
+      <c r="I61" s="6">
+        <v>22.36</v>
+      </c>
+      <c r="J61" s="18">
+        <v>45.12</v>
+      </c>
+      <c r="K61" s="18">
+        <v>45.42</v>
+      </c>
+      <c r="L61" s="18">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="M61" s="19">
+        <v>23</v>
+      </c>
+      <c r="N61" s="19"/>
+    </row>
+    <row r="62" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C62" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="16">
+        <v>96698</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-0.7</v>
+      </c>
+      <c r="I62" s="6">
+        <v>23.37</v>
+      </c>
+      <c r="J62" s="18">
+        <v>44.29</v>
+      </c>
+      <c r="K62" s="18">
+        <v>44.58</v>
+      </c>
+      <c r="L62" s="18">
+        <v>2.69</v>
+      </c>
+      <c r="M62" s="19">
+        <v>21.5</v>
+      </c>
+      <c r="N62" s="19"/>
+    </row>
+    <row r="63" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C63" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E63" s="16">
+        <v>125842</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-3.16</v>
+      </c>
+      <c r="I63" s="6">
+        <v>22.3</v>
+      </c>
+      <c r="J63" s="18">
+        <v>43.5</v>
+      </c>
+      <c r="K63" s="18">
+        <v>46</v>
+      </c>
+      <c r="L63" s="18">
+        <v>2.75</v>
+      </c>
+      <c r="M63" s="19">
+        <v>28</v>
+      </c>
+      <c r="N63" s="19"/>
+    </row>
+    <row r="64" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C64" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" s="16">
+        <v>192766</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="17">
+        <v>119.49</v>
+      </c>
+      <c r="H64" s="18">
+        <v>0.83</v>
+      </c>
+      <c r="I64" s="6">
+        <v>22.11</v>
+      </c>
+      <c r="J64" s="18">
+        <v>44.9</v>
+      </c>
+      <c r="K64" s="18">
+        <v>45.3</v>
+      </c>
+      <c r="L64" s="18">
+        <v>2.48</v>
+      </c>
+      <c r="M64" s="19">
+        <v>23.5</v>
+      </c>
+      <c r="N64" s="19"/>
+    </row>
+    <row r="65" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C65" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" s="16">
+        <v>193016</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-0.87</v>
+      </c>
+      <c r="I65" s="6">
+        <v>22.12</v>
+      </c>
+      <c r="J65" s="18">
+        <v>45.5</v>
+      </c>
+      <c r="K65" s="18">
+        <v>46</v>
+      </c>
+      <c r="L65" s="18">
+        <v>2.62</v>
+      </c>
+      <c r="M65" s="19">
+        <v>24.5</v>
+      </c>
+      <c r="N65" s="19"/>
+    </row>
+    <row r="66" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C66" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" s="16">
+        <v>10137</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H66" s="18">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="I66" s="6">
+        <v>22.78</v>
+      </c>
+      <c r="J66" s="18">
+        <v>44.47</v>
+      </c>
+      <c r="K66" s="18">
+        <v>45.49</v>
+      </c>
+      <c r="L66" s="18">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="M66" s="19">
+        <v>22.5</v>
+      </c>
+      <c r="N66" s="19"/>
+    </row>
+    <row r="67" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C67" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" s="16">
+        <v>198772</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H67" s="18">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I67" s="6">
+        <v>21.49</v>
+      </c>
+      <c r="J67" s="18">
+        <v>42.61</v>
+      </c>
+      <c r="K67" s="18">
+        <v>43.32</v>
+      </c>
+      <c r="L67" s="18">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="M67" s="19">
+        <v>28.5</v>
+      </c>
+      <c r="N67" s="19"/>
+    </row>
+    <row r="68" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C68" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="16">
+        <v>115099</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G68" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H68" s="18">
+        <v>-0.39</v>
+      </c>
+      <c r="I68" s="6">
+        <v>22.73</v>
+      </c>
+      <c r="J68" s="18">
+        <v>45.12</v>
+      </c>
+      <c r="K68" s="18">
+        <v>45.79</v>
+      </c>
+      <c r="L68" s="18">
+        <v>2.41</v>
+      </c>
+      <c r="M68" s="19">
+        <v>22</v>
+      </c>
+      <c r="N68" s="19"/>
+    </row>
+    <row r="69" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C69" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E69" s="16">
+        <v>207268</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G69" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H69" s="18">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I69" s="6">
+        <v>22.97</v>
+      </c>
+      <c r="J69" s="18">
+        <v>41.82</v>
+      </c>
+      <c r="K69" s="18">
+        <v>42.19</v>
+      </c>
+      <c r="L69" s="18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M69" s="19">
+        <v>24.5</v>
+      </c>
+      <c r="N69" s="19"/>
+    </row>
+    <row r="70" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C70" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" s="15">
+        <v>209451</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G70" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H70" s="18">
+        <v>-0.18</v>
+      </c>
+      <c r="I70" s="6">
+        <v>22.96</v>
+      </c>
+      <c r="J70" s="22">
+        <v>43.72</v>
+      </c>
+      <c r="K70" s="22">
+        <v>44.06</v>
+      </c>
+      <c r="L70" s="22">
+        <v>2.27</v>
+      </c>
+      <c r="M70" s="23">
+        <v>23</v>
+      </c>
+      <c r="N70" s="23"/>
+    </row>
+    <row r="71" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C71" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="15">
+        <v>46462</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G71" s="17">
+        <v>119.36</v>
+      </c>
+      <c r="H71" s="18">
+        <v>-0.73</v>
+      </c>
+      <c r="I71" s="6">
+        <v>22.56</v>
+      </c>
+      <c r="J71" s="22">
+        <v>44.53</v>
+      </c>
+      <c r="K71" s="22">
+        <v>45.42</v>
+      </c>
+      <c r="L71" s="22">
+        <v>2.29</v>
+      </c>
+      <c r="M71" s="23">
+        <v>24</v>
+      </c>
+      <c r="N71" s="23"/>
+    </row>
+    <row r="72" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C72" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" s="15">
+        <v>129805</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H72" s="18">
+        <v>1.74</v>
+      </c>
+      <c r="I72" s="10">
+        <v>20.83</v>
+      </c>
+      <c r="J72" s="22">
+        <v>44.23</v>
+      </c>
+      <c r="K72" s="22">
+        <v>44.94</v>
+      </c>
+      <c r="L72" s="22">
+        <v>2.27</v>
+      </c>
+      <c r="M72" s="23">
+        <v>30</v>
+      </c>
+      <c r="N72" s="23"/>
+    </row>
+    <row r="73" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C73" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="15">
+        <v>215513</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="17">
+        <v>118.98</v>
+      </c>
+      <c r="H73" s="18">
+        <v>-0.02</v>
+      </c>
+      <c r="I73" s="10">
+        <v>21.62</v>
+      </c>
+      <c r="J73" s="22">
+        <v>46.88</v>
+      </c>
+      <c r="K73" s="22">
+        <v>47.54</v>
+      </c>
+      <c r="L73" s="22">
+        <v>2.33</v>
+      </c>
+      <c r="M73" s="23">
+        <v>23.5</v>
+      </c>
+      <c r="N73" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Kanedata.xlsx
+++ b/Kanedata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAA7BB-46DA-4A95-BAB0-381FB2AA70BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F7D3F8-6854-45B8-BDC4-3275CD657154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="150" windowWidth="24060" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="870" windowWidth="24060" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="54">
   <si>
     <t>AConstant</t>
   </si>
@@ -206,10 +206,6 @@
   </si>
   <si>
     <t>attack36</t>
-  </si>
-  <si>
-    <t>KALF</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -260,18 +256,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -292,7 +282,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -334,33 +324,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -670,7 +633,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -2038,1302 +2001,6 @@
       </c>
       <c r="N37" s="14"/>
     </row>
-    <row r="38" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C38" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="16">
-        <v>105737</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H38" s="18">
-        <v>-0.61</v>
-      </c>
-      <c r="I38" s="6">
-        <v>23.04</v>
-      </c>
-      <c r="J38" s="18">
-        <v>44.75</v>
-      </c>
-      <c r="K38" s="18">
-        <v>44.25</v>
-      </c>
-      <c r="L38" s="18">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="M38" s="19">
-        <v>21.5</v>
-      </c>
-      <c r="N38" s="19"/>
-    </row>
-    <row r="39" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C39" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="16">
-        <v>133873</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H39" s="18">
-        <v>-0.62</v>
-      </c>
-      <c r="I39" s="6">
-        <v>22.79</v>
-      </c>
-      <c r="J39" s="18">
-        <v>43.75</v>
-      </c>
-      <c r="K39" s="18">
-        <v>44.5</v>
-      </c>
-      <c r="L39" s="18">
-        <v>1.81</v>
-      </c>
-      <c r="M39" s="19">
-        <v>22</v>
-      </c>
-      <c r="N39" s="19"/>
-    </row>
-    <row r="40" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C40" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="16">
-        <v>132594</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H40" s="18">
-        <v>-0.84</v>
-      </c>
-      <c r="I40" s="6">
-        <v>21.68</v>
-      </c>
-      <c r="J40" s="18">
-        <v>46.75</v>
-      </c>
-      <c r="K40" s="18">
-        <v>48.5</v>
-      </c>
-      <c r="L40" s="18">
-        <v>2.73</v>
-      </c>
-      <c r="M40" s="19">
-        <v>24.5</v>
-      </c>
-      <c r="N40" s="19"/>
-    </row>
-    <row r="41" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C41" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="16">
-        <v>133854</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H41" s="18">
-        <v>-2.04</v>
-      </c>
-      <c r="I41" s="6">
-        <v>21.05</v>
-      </c>
-      <c r="J41" s="18">
-        <v>47.75</v>
-      </c>
-      <c r="K41" s="18">
-        <v>48.5</v>
-      </c>
-      <c r="L41" s="18">
-        <v>1.98</v>
-      </c>
-      <c r="M41" s="19">
-        <v>27.5</v>
-      </c>
-      <c r="N41" s="19"/>
-    </row>
-    <row r="42" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C42" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="16">
-        <v>35135</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H42" s="18">
-        <v>1.83</v>
-      </c>
-      <c r="I42" s="6">
-        <v>21.78</v>
-      </c>
-      <c r="J42" s="18">
-        <v>42.56</v>
-      </c>
-      <c r="K42" s="18">
-        <v>43.44</v>
-      </c>
-      <c r="L42" s="18">
-        <v>3.16</v>
-      </c>
-      <c r="M42" s="19">
-        <v>25.5</v>
-      </c>
-      <c r="N42" s="19"/>
-    </row>
-    <row r="43" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C43" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="16">
-        <v>23574</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="17">
-        <v>118.5</v>
-      </c>
-      <c r="H43" s="18">
-        <v>-0.85</v>
-      </c>
-      <c r="I43" s="6">
-        <v>23.04</v>
-      </c>
-      <c r="J43" s="18">
-        <v>42.45</v>
-      </c>
-      <c r="K43" s="18">
-        <v>43.77</v>
-      </c>
-      <c r="L43" s="18">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="M43" s="19">
-        <v>23.5</v>
-      </c>
-      <c r="N43" s="19"/>
-    </row>
-    <row r="44" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C44" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="16">
-        <v>143993</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H44" s="18">
-        <v>-2.73</v>
-      </c>
-      <c r="I44" s="6">
-        <v>24.09</v>
-      </c>
-      <c r="J44" s="18">
-        <v>43.05</v>
-      </c>
-      <c r="K44" s="18">
-        <v>44.41</v>
-      </c>
-      <c r="L44" s="18">
-        <v>2.27</v>
-      </c>
-      <c r="M44" s="19">
-        <v>22.5</v>
-      </c>
-      <c r="N44" s="19"/>
-    </row>
-    <row r="45" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C45" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="16">
-        <v>47248</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H45" s="18">
-        <v>-0.4</v>
-      </c>
-      <c r="I45" s="6">
-        <v>22.17</v>
-      </c>
-      <c r="J45" s="18">
-        <v>43.44</v>
-      </c>
-      <c r="K45" s="18">
-        <v>44.7</v>
-      </c>
-      <c r="L45" s="18">
-        <v>2.06</v>
-      </c>
-      <c r="M45" s="19">
-        <v>26</v>
-      </c>
-      <c r="N45" s="19"/>
-    </row>
-    <row r="46" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C46" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="16">
-        <v>110627</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H46" s="18">
-        <v>0.32</v>
-      </c>
-      <c r="I46" s="6">
-        <v>21.69</v>
-      </c>
-      <c r="J46" s="18">
-        <v>43.72</v>
-      </c>
-      <c r="K46" s="18">
-        <v>45.3</v>
-      </c>
-      <c r="L46" s="18">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="M46" s="19">
-        <v>26.5</v>
-      </c>
-      <c r="N46" s="19"/>
-    </row>
-    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C47" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="16">
-        <v>161460</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G47" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H47" s="18">
-        <v>-0.72</v>
-      </c>
-      <c r="I47" s="6">
-        <v>23.65</v>
-      </c>
-      <c r="J47" s="18">
-        <v>41.62</v>
-      </c>
-      <c r="K47" s="18">
-        <v>43.16</v>
-      </c>
-      <c r="L47" s="18">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="M47" s="19">
-        <v>23</v>
-      </c>
-      <c r="N47" s="19"/>
-    </row>
-    <row r="48" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C48" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E48" s="16">
-        <v>161554</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H48" s="18">
-        <v>-0.72</v>
-      </c>
-      <c r="I48" s="6">
-        <v>21.55</v>
-      </c>
-      <c r="J48" s="18">
-        <v>44.64</v>
-      </c>
-      <c r="K48" s="18">
-        <v>46.81</v>
-      </c>
-      <c r="L48" s="18">
-        <v>2.37</v>
-      </c>
-      <c r="M48" s="19">
-        <v>26.5</v>
-      </c>
-      <c r="N48" s="19"/>
-    </row>
-    <row r="49" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C49" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E49" s="16">
-        <v>166237</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G49" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H49" s="18">
-        <v>-1.33</v>
-      </c>
-      <c r="I49" s="6">
-        <v>22.41</v>
-      </c>
-      <c r="J49" s="18">
-        <v>44.76</v>
-      </c>
-      <c r="K49" s="18">
-        <v>45.61</v>
-      </c>
-      <c r="L49" s="18">
-        <v>2.11</v>
-      </c>
-      <c r="M49" s="19">
-        <v>24.5</v>
-      </c>
-      <c r="N49" s="19"/>
-    </row>
-    <row r="50" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C50" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E50" s="16">
-        <v>166886</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G50" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H50" s="18">
-        <v>0.41</v>
-      </c>
-      <c r="I50" s="6">
-        <v>22.79</v>
-      </c>
-      <c r="J50" s="18">
-        <v>41.56</v>
-      </c>
-      <c r="K50" s="18">
-        <v>42.51</v>
-      </c>
-      <c r="L50" s="18">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M50" s="19">
-        <v>25</v>
-      </c>
-      <c r="N50" s="19"/>
-    </row>
-    <row r="51" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C51" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51" s="16">
-        <v>167592</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H51" s="18">
-        <v>-1.67</v>
-      </c>
-      <c r="I51" s="6">
-        <v>22.61</v>
-      </c>
-      <c r="J51" s="18">
-        <v>43.44</v>
-      </c>
-      <c r="K51" s="18">
-        <v>45.67</v>
-      </c>
-      <c r="L51" s="18">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="M51" s="19">
-        <v>25.5</v>
-      </c>
-      <c r="N51" s="19"/>
-    </row>
-    <row r="52" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C52" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="16">
-        <v>51973</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H52" s="18">
-        <v>0.16</v>
-      </c>
-      <c r="I52" s="6">
-        <v>21.25</v>
-      </c>
-      <c r="J52" s="18">
-        <v>44.76</v>
-      </c>
-      <c r="K52" s="18">
-        <v>47.47</v>
-      </c>
-      <c r="L52" s="18">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="M52" s="19">
-        <v>26</v>
-      </c>
-      <c r="N52" s="19"/>
-    </row>
-    <row r="53" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C53" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="16">
-        <v>145550</v>
-      </c>
-      <c r="F53" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H53" s="18">
-        <v>-0.08</v>
-      </c>
-      <c r="I53" s="6">
-        <v>22.04</v>
-      </c>
-      <c r="J53" s="18">
-        <v>44.41</v>
-      </c>
-      <c r="K53" s="18">
-        <v>44.76</v>
-      </c>
-      <c r="L53" s="18">
-        <v>2.35</v>
-      </c>
-      <c r="M53" s="19">
-        <v>25.5</v>
-      </c>
-      <c r="N53" s="19"/>
-    </row>
-    <row r="54" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C54" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E54" s="16">
-        <v>173959</v>
-      </c>
-      <c r="F54" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" s="17">
-        <v>119.49</v>
-      </c>
-      <c r="H54" s="18">
-        <v>-1.35</v>
-      </c>
-      <c r="I54" s="6">
-        <v>22.75</v>
-      </c>
-      <c r="J54" s="18">
-        <v>43.49</v>
-      </c>
-      <c r="K54" s="18">
-        <v>44.18</v>
-      </c>
-      <c r="L54" s="18">
-        <v>2.33</v>
-      </c>
-      <c r="M54" s="19">
-        <v>25.5</v>
-      </c>
-      <c r="N54" s="19"/>
-    </row>
-    <row r="55" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C55" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E55" s="16">
-        <v>174163</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H55" s="18">
-        <v>-1.6</v>
-      </c>
-      <c r="I55" s="6">
-        <v>22.47</v>
-      </c>
-      <c r="J55" s="18">
-        <v>43.44</v>
-      </c>
-      <c r="K55" s="18">
-        <v>45.24</v>
-      </c>
-      <c r="L55" s="18">
-        <v>1.83</v>
-      </c>
-      <c r="M55" s="19">
-        <v>25.5</v>
-      </c>
-      <c r="N55" s="19"/>
-    </row>
-    <row r="56" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C56" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E56" s="16">
-        <v>28886</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G56" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H56" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="I56" s="6">
-        <v>21.53</v>
-      </c>
-      <c r="J56" s="18">
-        <v>46.36</v>
-      </c>
-      <c r="K56" s="18">
-        <v>47.67</v>
-      </c>
-      <c r="L56" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="M56" s="19">
-        <v>24.5</v>
-      </c>
-      <c r="N56" s="19"/>
-    </row>
-    <row r="57" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C57" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E57" s="16">
-        <v>177432</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H57" s="18">
-        <v>-0.87</v>
-      </c>
-      <c r="I57" s="6">
-        <v>22.97</v>
-      </c>
-      <c r="J57" s="18">
-        <v>44.7</v>
-      </c>
-      <c r="K57" s="18">
-        <v>45.61</v>
-      </c>
-      <c r="L57" s="18">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M57" s="19">
-        <v>22.5</v>
-      </c>
-      <c r="N57" s="19"/>
-    </row>
-    <row r="58" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C58" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E58" s="16">
-        <v>178621</v>
-      </c>
-      <c r="F58" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H58" s="18">
-        <v>-0.02</v>
-      </c>
-      <c r="I58" s="6">
-        <v>21.95</v>
-      </c>
-      <c r="J58" s="18">
-        <v>45.98</v>
-      </c>
-      <c r="K58" s="18">
-        <v>46.87</v>
-      </c>
-      <c r="L58" s="18">
-        <v>2.13</v>
-      </c>
-      <c r="M58" s="19">
-        <v>23.5</v>
-      </c>
-      <c r="N58" s="19"/>
-    </row>
-    <row r="59" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C59" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E59" s="16">
-        <v>178965</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H59" s="18">
-        <v>-1.1200000000000001</v>
-      </c>
-      <c r="I59" s="6">
-        <v>22.03</v>
-      </c>
-      <c r="J59" s="18">
-        <v>43.95</v>
-      </c>
-      <c r="K59" s="18">
-        <v>44.23</v>
-      </c>
-      <c r="L59" s="18">
-        <v>2.19</v>
-      </c>
-      <c r="M59" s="19">
-        <v>27</v>
-      </c>
-      <c r="N59" s="19"/>
-    </row>
-    <row r="60" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C60" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E60" s="16">
-        <v>184985</v>
-      </c>
-      <c r="F60" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H60" s="18">
-        <v>0.52</v>
-      </c>
-      <c r="I60" s="6">
-        <v>21.58</v>
-      </c>
-      <c r="J60" s="18">
-        <v>43.55</v>
-      </c>
-      <c r="K60" s="18">
-        <v>45.79</v>
-      </c>
-      <c r="L60" s="18">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="M60" s="19">
-        <v>26</v>
-      </c>
-      <c r="N60" s="19"/>
-    </row>
-    <row r="61" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C61" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E61" s="16">
-        <v>186160</v>
-      </c>
-      <c r="F61" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H61" s="18">
-        <v>-0.06</v>
-      </c>
-      <c r="I61" s="6">
-        <v>22.36</v>
-      </c>
-      <c r="J61" s="18">
-        <v>45.12</v>
-      </c>
-      <c r="K61" s="18">
-        <v>45.42</v>
-      </c>
-      <c r="L61" s="18">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="M61" s="19">
-        <v>23</v>
-      </c>
-      <c r="N61" s="19"/>
-    </row>
-    <row r="62" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C62" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E62" s="16">
-        <v>96698</v>
-      </c>
-      <c r="F62" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G62" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H62" s="18">
-        <v>-0.7</v>
-      </c>
-      <c r="I62" s="6">
-        <v>23.37</v>
-      </c>
-      <c r="J62" s="18">
-        <v>44.29</v>
-      </c>
-      <c r="K62" s="18">
-        <v>44.58</v>
-      </c>
-      <c r="L62" s="18">
-        <v>2.69</v>
-      </c>
-      <c r="M62" s="19">
-        <v>21.5</v>
-      </c>
-      <c r="N62" s="19"/>
-    </row>
-    <row r="63" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C63" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E63" s="16">
-        <v>125842</v>
-      </c>
-      <c r="F63" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G63" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H63" s="18">
-        <v>-3.16</v>
-      </c>
-      <c r="I63" s="6">
-        <v>22.3</v>
-      </c>
-      <c r="J63" s="18">
-        <v>43.5</v>
-      </c>
-      <c r="K63" s="18">
-        <v>46</v>
-      </c>
-      <c r="L63" s="18">
-        <v>2.75</v>
-      </c>
-      <c r="M63" s="19">
-        <v>28</v>
-      </c>
-      <c r="N63" s="19"/>
-    </row>
-    <row r="64" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C64" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E64" s="16">
-        <v>192766</v>
-      </c>
-      <c r="F64" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G64" s="17">
-        <v>119.49</v>
-      </c>
-      <c r="H64" s="18">
-        <v>0.83</v>
-      </c>
-      <c r="I64" s="6">
-        <v>22.11</v>
-      </c>
-      <c r="J64" s="18">
-        <v>44.9</v>
-      </c>
-      <c r="K64" s="18">
-        <v>45.3</v>
-      </c>
-      <c r="L64" s="18">
-        <v>2.48</v>
-      </c>
-      <c r="M64" s="19">
-        <v>23.5</v>
-      </c>
-      <c r="N64" s="19"/>
-    </row>
-    <row r="65" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C65" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E65" s="16">
-        <v>193016</v>
-      </c>
-      <c r="F65" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G65" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H65" s="18">
-        <v>-0.87</v>
-      </c>
-      <c r="I65" s="6">
-        <v>22.12</v>
-      </c>
-      <c r="J65" s="18">
-        <v>45.5</v>
-      </c>
-      <c r="K65" s="18">
-        <v>46</v>
-      </c>
-      <c r="L65" s="18">
-        <v>2.62</v>
-      </c>
-      <c r="M65" s="19">
-        <v>24.5</v>
-      </c>
-      <c r="N65" s="19"/>
-    </row>
-    <row r="66" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C66" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E66" s="16">
-        <v>10137</v>
-      </c>
-      <c r="F66" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H66" s="18">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="I66" s="6">
-        <v>22.78</v>
-      </c>
-      <c r="J66" s="18">
-        <v>44.47</v>
-      </c>
-      <c r="K66" s="18">
-        <v>45.49</v>
-      </c>
-      <c r="L66" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="M66" s="19">
-        <v>22.5</v>
-      </c>
-      <c r="N66" s="19"/>
-    </row>
-    <row r="67" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C67" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E67" s="16">
-        <v>198772</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G67" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H67" s="18">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="I67" s="6">
-        <v>21.49</v>
-      </c>
-      <c r="J67" s="18">
-        <v>42.61</v>
-      </c>
-      <c r="K67" s="18">
-        <v>43.32</v>
-      </c>
-      <c r="L67" s="18">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="M67" s="19">
-        <v>28.5</v>
-      </c>
-      <c r="N67" s="19"/>
-    </row>
-    <row r="68" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C68" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E68" s="16">
-        <v>115099</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G68" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H68" s="18">
-        <v>-0.39</v>
-      </c>
-      <c r="I68" s="6">
-        <v>22.73</v>
-      </c>
-      <c r="J68" s="18">
-        <v>45.12</v>
-      </c>
-      <c r="K68" s="18">
-        <v>45.79</v>
-      </c>
-      <c r="L68" s="18">
-        <v>2.41</v>
-      </c>
-      <c r="M68" s="19">
-        <v>22</v>
-      </c>
-      <c r="N68" s="19"/>
-    </row>
-    <row r="69" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C69" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E69" s="16">
-        <v>207268</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G69" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H69" s="18">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="I69" s="6">
-        <v>22.97</v>
-      </c>
-      <c r="J69" s="18">
-        <v>41.82</v>
-      </c>
-      <c r="K69" s="18">
-        <v>42.19</v>
-      </c>
-      <c r="L69" s="18">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M69" s="19">
-        <v>24.5</v>
-      </c>
-      <c r="N69" s="19"/>
-    </row>
-    <row r="70" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C70" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E70" s="15">
-        <v>209451</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G70" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H70" s="18">
-        <v>-0.18</v>
-      </c>
-      <c r="I70" s="6">
-        <v>22.96</v>
-      </c>
-      <c r="J70" s="22">
-        <v>43.72</v>
-      </c>
-      <c r="K70" s="22">
-        <v>44.06</v>
-      </c>
-      <c r="L70" s="22">
-        <v>2.27</v>
-      </c>
-      <c r="M70" s="23">
-        <v>23</v>
-      </c>
-      <c r="N70" s="23"/>
-    </row>
-    <row r="71" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C71" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="15">
-        <v>46462</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G71" s="17">
-        <v>119.36</v>
-      </c>
-      <c r="H71" s="18">
-        <v>-0.73</v>
-      </c>
-      <c r="I71" s="6">
-        <v>22.56</v>
-      </c>
-      <c r="J71" s="22">
-        <v>44.53</v>
-      </c>
-      <c r="K71" s="22">
-        <v>45.42</v>
-      </c>
-      <c r="L71" s="22">
-        <v>2.29</v>
-      </c>
-      <c r="M71" s="23">
-        <v>24</v>
-      </c>
-      <c r="N71" s="23"/>
-    </row>
-    <row r="72" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C72" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="15">
-        <v>129805</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H72" s="18">
-        <v>1.74</v>
-      </c>
-      <c r="I72" s="10">
-        <v>20.83</v>
-      </c>
-      <c r="J72" s="22">
-        <v>44.23</v>
-      </c>
-      <c r="K72" s="22">
-        <v>44.94</v>
-      </c>
-      <c r="L72" s="22">
-        <v>2.27</v>
-      </c>
-      <c r="M72" s="23">
-        <v>30</v>
-      </c>
-      <c r="N72" s="23"/>
-    </row>
-    <row r="73" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C73" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="15">
-        <v>215513</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" s="17">
-        <v>118.98</v>
-      </c>
-      <c r="H73" s="18">
-        <v>-0.02</v>
-      </c>
-      <c r="I73" s="10">
-        <v>21.62</v>
-      </c>
-      <c r="J73" s="22">
-        <v>46.88</v>
-      </c>
-      <c r="K73" s="22">
-        <v>47.54</v>
-      </c>
-      <c r="L73" s="22">
-        <v>2.33</v>
-      </c>
-      <c r="M73" s="23">
-        <v>23.5</v>
-      </c>
-      <c r="N73" s="23"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
